--- a/Data/Solar Power.xlsx
+++ b/Data/Solar Power.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9342E926-E13F-6845-9BFF-6209BB9199EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ABAEFF-EB02-7743-82A5-2E95C8B6F9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="119">
   <si>
     <t>Metrics</t>
   </si>
@@ -2761,7 +2761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5344E307-70EA-9749-BC3D-54A83804696F}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
@@ -2817,271 +2817,248 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>21.17</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>21.17</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>21.17</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21.17</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>21.17</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>21.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>5.0000000000000001E-3</v>
+        <v>156.03754062836398</v>
       </c>
       <c r="C6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G6">
-        <v>5.0000000000000001E-3</v>
-      </c>
+        <v>312.07508125672797</v>
+      </c>
+      <c r="D6" s="4">
+        <v>5011.5586578286311</v>
+      </c>
+      <c r="E6" s="4">
+        <v>10023.117315657262</v>
+      </c>
+      <c r="F6" s="4">
+        <v>50115.586578286311</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100231.17315657262</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>156.03754062836398</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>312.07508125672797</v>
-      </c>
-      <c r="D7" s="4">
-        <v>5011.5586578286311</v>
-      </c>
-      <c r="E7" s="4">
-        <v>10023.117315657262</v>
-      </c>
-      <c r="F7" s="4">
-        <v>50115.586578286311</v>
-      </c>
-      <c r="G7" s="4">
-        <v>100231.17315657262</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <f>(1-0.58)/B4</f>
+        <v>1.6800000000000002E-2</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <f t="shared" ref="C8:G8" si="0">(1-0.58)/C4</f>
+        <v>1.6800000000000002E-2</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>1.6800000000000002E-2</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>1.6800000000000002E-2</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>1.6800000000000002E-2</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>1.6800000000000002E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9">
-        <f>(1-0.58)/B5</f>
-        <v>1.6800000000000002E-2</v>
+        <f>B2*0.58</f>
+        <v>11627.312199999998</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:G9" si="0">(1-0.58)/C5</f>
-        <v>1.6800000000000002E-2</v>
+        <f>C2*0.58</f>
+        <v>18890.733399999997</v>
       </c>
       <c r="D9">
-        <f t="shared" si="0"/>
-        <v>1.6800000000000002E-2</v>
+        <f t="shared" ref="D9:E9" si="1">D2*0.58</f>
+        <v>366410.56299999997</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
-        <v>1.6800000000000002E-2</v>
+        <f t="shared" si="1"/>
+        <v>548260.0567999999</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
-        <v>1.6800000000000002E-2</v>
+        <f>F2*0.58</f>
+        <v>1850298.8551999999</v>
       </c>
       <c r="G9">
-        <f t="shared" si="0"/>
-        <v>1.6800000000000002E-2</v>
-      </c>
+        <f>G2*0.58</f>
+        <v>3382670.3275999995</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <f>B2*0.58</f>
-        <v>11627.312199999998</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <f>C2*0.58</f>
-        <v>18890.733399999997</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <f t="shared" ref="D10:E10" si="1">D2*0.58</f>
-        <v>366410.56299999997</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <f t="shared" si="1"/>
-        <v>548260.0567999999</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <f>F2*0.58</f>
-        <v>1850298.8551999999</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <f>G2*0.58</f>
-        <v>3382670.3275999995</v>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.91825292799460578</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.91825292799460578</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.91825292799460578</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.91825292799460578</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.91825292799460578</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.91825292799460578</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B12">
-        <v>0.91825292799460578</v>
+        <v>88</v>
       </c>
       <c r="C12">
-        <v>0.91825292799460578</v>
+        <v>177</v>
       </c>
       <c r="D12">
-        <v>0.91825292799460578</v>
+        <v>2837</v>
       </c>
       <c r="E12">
-        <v>0.91825292799460578</v>
+        <v>5674</v>
       </c>
       <c r="F12">
-        <v>0.91825292799460578</v>
+        <v>28370</v>
       </c>
       <c r="G12">
-        <v>0.91825292799460578</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B13">
-        <v>88</v>
-      </c>
-      <c r="C13">
-        <v>177</v>
-      </c>
-      <c r="D13">
-        <v>2837</v>
-      </c>
-      <c r="E13">
-        <v>5674</v>
-      </c>
-      <c r="F13">
-        <v>28370</v>
-      </c>
-      <c r="G13">
         <v>56739</v>
       </c>
     </row>
@@ -5443,22 +5420,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="F19:G19"/>
@@ -5468,6 +5429,22 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="H10:I10"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F64:G64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Data/Solar Power.xlsx
+++ b/Data/Solar Power.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ABAEFF-EB02-7743-82A5-2E95C8B6F9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F17DC1-4CE4-A142-B6A7-205B5A44D0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -3429,13 +3429,13 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.3125</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="C2">
-        <v>0.375</v>
+        <v>0.38461538461538458</v>
       </c>
       <c r="D2">
-        <v>0.3125</v>
+        <v>0.30769230769230771</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3443,13 +3443,13 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.15575314059699699</v>
+        <v>8.9656651833328549E-2</v>
       </c>
       <c r="C3">
-        <v>7.0960339119032198E-2</v>
+        <v>0.33610253300006032</v>
       </c>
       <c r="D3">
-        <v>1.9499099067965001E-2</v>
+        <v>0.62607499299999958</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3457,13 +3457,13 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>2.6959580160185601E-2</v>
+        <v>4.0844230038268023E-2</v>
       </c>
       <c r="C4">
-        <v>4.1532217357839199E-2</v>
+        <v>0.1202687349999242</v>
       </c>
       <c r="D4">
-        <v>8.1027352375768796E-4</v>
+        <v>0.110505985000003</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -3471,16 +3471,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <f>EXP(-B3*5)</f>
-        <v>0.45897216980863992</v>
+        <v>0.91424503574506411</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:D5" si="0">EXP(-C3*5)</f>
-        <v>0.70131250277852375</v>
+        <v>0.7145498371213993</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0.90710642775279782</v>
+        <v>0.53468633539608523</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3488,16 +3485,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <f>EXP(B4*5)</f>
-        <v>1.1443054977560938</v>
+        <v>1.0416898289221079</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:D6" si="1">EXP(C4*5)</f>
-        <v>1.2307959658423091</v>
+        <v>1.127799890162412</v>
       </c>
       <c r="D6">
-        <f t="shared" si="1"/>
-        <v>1.0040595855027215</v>
+        <v>1.1168430333376731</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -3543,12 +3537,10 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <f>10/16</f>
-        <v>0.625</v>
+        <v>0.38461538461538458</v>
       </c>
       <c r="C2">
-        <f>6/16</f>
-        <v>0.375</v>
+        <v>0.61538461538461542</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3556,10 +3548,10 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>3.7907085514064499E-2</v>
+        <v>0.1019332660000004</v>
       </c>
       <c r="C3">
-        <v>0.15446755600000001</v>
+        <v>0.46393994884651818</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3567,10 +3559,10 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>2.0528048904587998E-2</v>
+        <v>3.8151803000000352E-2</v>
       </c>
       <c r="C4">
-        <v>2.9158527999998501E-2</v>
+        <v>9.9125460236833537E-2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -3578,12 +3570,10 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <f>EXP(-5*B3)</f>
-        <v>0.82734340561156228</v>
+        <v>0.90308981645381026</v>
       </c>
       <c r="C5">
-        <f>EXP(-5*C3)</f>
-        <v>0.46193190986808103</v>
+        <v>0.62880131357753921</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3591,12 +3581,10 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <f>EXP(B4*5)</f>
-        <v>1.1080926949444148</v>
+        <v>1.0388889273647881</v>
       </c>
       <c r="C6">
-        <f>EXP(C4*5)</f>
-        <v>1.1569562567261729</v>
+        <v>1.1042048246678191</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -5420,6 +5408,22 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="F19:G19"/>
@@ -5429,22 +5433,6 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="H10:I10"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F64:G64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Data/Solar Power.xlsx
+++ b/Data/Solar Power.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F17DC1-4CE4-A142-B6A7-205B5A44D0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA83C6BB-7668-DE46-981D-F84BC271838F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="117">
   <si>
     <t>Metrics</t>
   </si>
@@ -310,27 +310,6 @@
     <t>O&amp;M Cost 2024$/year</t>
   </si>
   <si>
-    <t>'''</t>
-  </si>
-  <si>
-    <t>x[0,0] = 0.026959580160185622 x[1,0] = 0.15575314059699774</t>
-  </si>
-  <si>
-    <t>x[0,1] = 0.04153221735783926 x[1,1] = 0.07096033911903228</t>
-  </si>
-  <si>
-    <t>x[0,2] = 0.0008102735237576885 x[1,2] = 0.019499099067965004</t>
-  </si>
-  <si>
-    <t>Geometric median: [0.02661469 0.1556113 ]</t>
-  </si>
-  <si>
-    <t>Geometric median: [0.041811 0.07124102]</t>
-  </si>
-  <si>
-    <t>Geometric median: [0.00039564 0.01923379]</t>
-  </si>
-  <si>
     <t>2 MPPT</t>
   </si>
   <si>
@@ -398,13 +377,34 @@
   </si>
   <si>
     <t>Spatial requirement</t>
+  </si>
+  <si>
+    <t>tts 2019 report</t>
+  </si>
+  <si>
+    <t>Installation Price $/W</t>
+  </si>
+  <si>
+    <t>Median Module Efficiency</t>
+  </si>
+  <si>
+    <t>Mid-Scale Non-Residential Installations</t>
+  </si>
+  <si>
+    <t>2022 Usd to 2024 Usd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.00000000"/>
+    <numFmt numFmtId="165" formatCode="0.0000000"/>
+    <numFmt numFmtId="166" formatCode="0.000000000"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -438,8 +438,15 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF448C27"/>
-      <name val="Menlo"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -460,12 +467,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -474,14 +482,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1226,6 +1240,431 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-TR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Extras2!$H$42:$H$64</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2040</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Extras2!$I$42:$I$64</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>11.186864000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.649034</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.326336</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.326336</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.8960720000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.4155621395835229</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.9583837308740915</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.5234039008890665</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.1095447839900103</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.7157808509672696</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.3411363678124966</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.9846829778820361</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.6455374014598512</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.322859247019589</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.0158489287621615</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.7237456852685691</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.4458256943582546</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.1814002794816698</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.929814203202552</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.6904440435412207</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.4626966491555198</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.2460076695314015</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.039840156541012</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D45A-8842-BCB6-B0EB443D24F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="106526223"/>
+        <c:axId val="106527935"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="106526223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="106527935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="106527935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="106526223"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-TR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1306,6 +1745,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -1823,6 +2302,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2381,61 +3376,17 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>152127</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>39056</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>129484</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>513871</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>17804</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8D15669-7D06-2D71-AE54-642BE4C36457}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7581627" y="242256"/>
-          <a:ext cx="7791244" cy="5261948"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>527050</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>146050</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>576745</xdr:colOff>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2444,6 +3395,42 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFA49936-B4A5-E409-54EF-9C2BA9047519}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>364435</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>146879</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>795130</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>107122</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCF8B0E2-3660-6FEB-AEDF-75451A9D3615}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2794,26 +3781,26 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>20047.09</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>32570.23</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>631742.35</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>945275.96</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>3190170.44</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>5832190.2199999997</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -2894,21 +3881,21 @@
       <c r="C6">
         <v>312.07508125672797</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>5011.5586578286311</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>10023.117315657262</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>50115.586578286311</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>100231.17315657262</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -2990,8 +3977,8 @@
         <f>G2*0.58</f>
         <v>3382670.3275999995</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -3018,7 +4005,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B11">
         <v>0.91825292799460578</v>
@@ -3041,7 +4028,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B12">
         <v>88</v>
@@ -3102,26 +4089,26 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>20047.09</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>32570.23</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>631742.35</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>945275.96</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>3190170.44</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>5832190.2199999997</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -3248,21 +4235,21 @@
       <c r="C8">
         <v>312.07508125672797</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>5011.5586578286311</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>10023.117315657262</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>50115.586578286311</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>100231.17315657262</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -3338,8 +4325,8 @@
         <f>G2*0.58</f>
         <v>3382670.3275999995</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -3366,7 +4353,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B13">
         <v>0.91825292799460578</v>
@@ -3429,13 +4416,13 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.30769230769230771</v>
+        <v>0.30769230769230699</v>
       </c>
       <c r="C2">
-        <v>0.38461538461538458</v>
+        <v>0.38461538461538403</v>
       </c>
       <c r="D2">
-        <v>0.30769230769230771</v>
+        <v>0.30769230769230699</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3443,13 +4430,13 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>8.9656651833328549E-2</v>
+        <v>8.6254240897454204E-2</v>
       </c>
       <c r="C3">
-        <v>0.33610253300006032</v>
+        <v>0.35211674781527602</v>
       </c>
       <c r="D3">
-        <v>0.62607499299999958</v>
+        <v>0.59445630266358296</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3457,13 +4444,13 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>4.0844230038268023E-2</v>
+        <v>4.3455814737737103E-2</v>
       </c>
       <c r="C4">
-        <v>0.1202687349999242</v>
+        <v>9.7984650020579406E-2</v>
       </c>
       <c r="D4">
-        <v>0.110505985000003</v>
+        <v>9.9477333500993401E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -3471,13 +4458,16 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.91424503574506411</v>
+        <f>EXP(-B3)</f>
+        <v>0.91736097089272073</v>
       </c>
       <c r="C5">
-        <v>0.7145498371213993</v>
+        <f t="shared" ref="C5:D5" si="0">EXP(-C3)</f>
+        <v>0.70319802035125911</v>
       </c>
       <c r="D5">
-        <v>0.53468633539608523</v>
+        <f t="shared" si="0"/>
+        <v>0.55186253050335687</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3485,13 +4475,16 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1.0416898289221079</v>
+        <f>EXP(B4)</f>
+        <v>1.0444138455928085</v>
       </c>
       <c r="C6">
-        <v>1.127799890162412</v>
+        <f t="shared" ref="C6:D6" si="1">EXP(C4)</f>
+        <v>1.1029458547823952</v>
       </c>
       <c r="D6">
-        <v>1.1168430333376731</v>
+        <f t="shared" si="1"/>
+        <v>1.1045934331902412</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -3515,13 +4508,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4491238B-0F4C-1343-88A8-2D1E4AFF318E}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3532,62 +4525,67 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.38461538461538458</v>
+        <v>0.53846153846153799</v>
       </c>
       <c r="C2">
-        <v>0.61538461538461542</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>0.46153846153846101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.1019332660000004</v>
+        <v>0.178442608367122</v>
       </c>
       <c r="C3">
-        <v>0.46393994884651818</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>0.53962817583231903</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4">
-        <v>3.8151803000000352E-2</v>
-      </c>
-      <c r="C4">
-        <v>9.9125460236833537E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>7.0487389258451605E-2</v>
+      </c>
+      <c r="C4" s="13">
+        <v>9.4514289570146903E-2</v>
+      </c>
+      <c r="D4" s="13"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.90308981645381026</v>
+        <f>EXP(-B3)</f>
+        <v>0.83657206773665604</v>
       </c>
       <c r="C5">
-        <v>0.62880131357753921</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <f>EXP(-C3)</f>
+        <v>0.5829649725462982</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1.0388889273647881</v>
+        <f>EXP(B4)</f>
+        <v>1.0730310376283012</v>
       </c>
       <c r="C6">
-        <v>1.1042048246678191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <f>EXP(C4)</f>
+        <v>1.0991248690426909</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3627,20 +4625,20 @@
       <c r="C1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="12"/>
+      <c r="H1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="10"/>
+      <c r="I1" s="12"/>
       <c r="K1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -3752,20 +4750,20 @@
       <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10" t="s">
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10" t="s">
+      <c r="G10" s="12"/>
+      <c r="H10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="10"/>
+      <c r="I10" s="12"/>
       <c r="K10" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -3877,18 +4875,18 @@
       <c r="C19" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10" t="s">
+      <c r="E19" s="12"/>
+      <c r="F19" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10" t="s">
+      <c r="G19" s="12"/>
+      <c r="H19" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="10"/>
+      <c r="I19" s="12"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
@@ -3999,18 +4997,18 @@
       <c r="C28" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10" t="s">
+      <c r="E28" s="12"/>
+      <c r="F28" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10" t="s">
+      <c r="G28" s="12"/>
+      <c r="H28" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="I28" s="10"/>
+      <c r="I28" s="12"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -4121,18 +5119,18 @@
       <c r="C37" t="s">
         <v>59</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10" t="s">
+      <c r="E37" s="12"/>
+      <c r="F37" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10" t="s">
+      <c r="G37" s="12"/>
+      <c r="H37" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="I37" s="10"/>
+      <c r="I37" s="12"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -4243,18 +5241,18 @@
       <c r="C46" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10" t="s">
+      <c r="E46" s="12"/>
+      <c r="F46" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10" t="s">
+      <c r="G46" s="12"/>
+      <c r="H46" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="I46" s="10"/>
+      <c r="I46" s="12"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
@@ -4365,18 +5363,18 @@
       <c r="C55" t="s">
         <v>59</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10" t="s">
+      <c r="E55" s="12"/>
+      <c r="F55" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10" t="s">
+      <c r="G55" s="12"/>
+      <c r="H55" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I55" s="10"/>
+      <c r="I55" s="12"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
@@ -4487,18 +5485,18 @@
       <c r="C64" t="s">
         <v>59</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="D64" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10" t="s">
+      <c r="E64" s="12"/>
+      <c r="F64" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10" t="s">
+      <c r="G64" s="12"/>
+      <c r="H64" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I64" s="10"/>
+      <c r="I64" s="12"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
@@ -4600,13 +5598,13 @@
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="Q68" s="9"/>
+      <c r="Q68" s="7"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="P71" s="9"/>
+      <c r="P71" s="7"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="P72" s="9"/>
+      <c r="P72" s="7"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
@@ -4621,7 +5619,7 @@
       <c r="E75" t="s">
         <v>82</v>
       </c>
-      <c r="I75" s="6" t="s">
+      <c r="I75" s="5" t="s">
         <v>83</v>
       </c>
       <c r="J75" t="s">
@@ -4630,8 +5628,8 @@
       <c r="K75" t="s">
         <v>88</v>
       </c>
-      <c r="O75" s="9"/>
-      <c r="Q75" s="9"/>
+      <c r="O75" s="7"/>
+      <c r="Q75" s="7"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
@@ -4657,18 +5655,18 @@
         <f>_xlfn.TEXTJOIN(",", TRUE, B76, C76, D76, E76)</f>
         <v>5141.32,8237.06,9591.94,5914.83</v>
       </c>
-      <c r="I76" s="4">
+      <c r="I76" s="3">
         <v>18.7</v>
       </c>
-      <c r="J76" s="4">
+      <c r="J76" s="3">
         <v>20047.09</v>
       </c>
       <c r="K76">
         <f>I76*$C$95</f>
         <v>156.03754062836398</v>
       </c>
-      <c r="O76" s="9"/>
-      <c r="Q76" s="9"/>
+      <c r="O76" s="7"/>
+      <c r="Q76" s="7"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
@@ -4694,18 +5692,18 @@
         <f t="shared" ref="F77:F83" si="0">_xlfn.TEXTJOIN(",", TRUE, B77, C77, D77, E77)</f>
         <v>10651.71,16658.78,19408.82,12082.68</v>
       </c>
-      <c r="I77" s="4">
+      <c r="I77" s="3">
         <v>37.4</v>
       </c>
-      <c r="J77" s="4">
+      <c r="J77" s="3">
         <v>32570.23</v>
       </c>
       <c r="K77">
         <f t="shared" ref="K77:K83" si="1">I77*$C$95</f>
         <v>312.07508125672797</v>
       </c>
-      <c r="O77" s="9"/>
-      <c r="Q77" s="9"/>
+      <c r="O77" s="7"/>
+      <c r="Q77" s="7"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
@@ -4731,18 +5729,18 @@
         <f t="shared" si="0"/>
         <v>26553.22,41479.7,48327.1,30086.78</v>
       </c>
-      <c r="I78" s="4">
+      <c r="I78" s="3">
         <v>93.5</v>
       </c>
-      <c r="J78" s="4">
+      <c r="J78" s="3">
         <v>59337.98</v>
       </c>
       <c r="K78">
         <f t="shared" si="1"/>
         <v>780.18770314181984</v>
       </c>
-      <c r="O78" s="9"/>
-      <c r="Q78" s="9"/>
+      <c r="O78" s="7"/>
+      <c r="Q78" s="7"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
@@ -4768,18 +5766,18 @@
         <f t="shared" si="0"/>
         <v>47351.1,74607.7,86964.1,54097.2</v>
       </c>
-      <c r="I79" s="4">
+      <c r="I79" s="3">
         <v>168.3</v>
       </c>
-      <c r="J79" s="4">
+      <c r="J79" s="3">
         <v>88896.68</v>
       </c>
       <c r="K79">
         <f t="shared" si="1"/>
         <v>1404.3378656552759</v>
       </c>
-      <c r="O79" s="9"/>
-      <c r="Q79" s="9"/>
+      <c r="O79" s="7"/>
+      <c r="Q79" s="7"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
@@ -4805,18 +5803,18 @@
         <f t="shared" si="0"/>
         <v>173325.4,275416.2,318744.5,195308.2</v>
       </c>
-      <c r="I80" s="4">
+      <c r="I80" s="3">
         <v>600.6</v>
       </c>
-      <c r="J80" s="4">
+      <c r="J80" s="3">
         <v>631742.35</v>
       </c>
       <c r="K80">
         <f t="shared" si="1"/>
         <v>5011.5586578286311</v>
       </c>
-      <c r="O80" s="9"/>
-      <c r="Q80" s="9"/>
+      <c r="O80" s="7"/>
+      <c r="Q80" s="7"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
@@ -4842,18 +5840,18 @@
         <f t="shared" si="0"/>
         <v>346650.2,550832,637491,390616.1</v>
       </c>
-      <c r="I81" s="4">
+      <c r="I81" s="3">
         <v>1201.2</v>
       </c>
-      <c r="J81" s="4">
+      <c r="J81" s="3">
         <v>945275.96</v>
       </c>
       <c r="K81">
         <f t="shared" si="1"/>
         <v>10023.117315657262</v>
       </c>
-      <c r="O81" s="9"/>
-      <c r="Q81" s="9"/>
+      <c r="O81" s="7"/>
+      <c r="Q81" s="7"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
@@ -4879,18 +5877,18 @@
         <f t="shared" si="0"/>
         <v>1733254,2754162,3187445,1953082</v>
       </c>
-      <c r="I82" s="4">
+      <c r="I82" s="3">
         <v>6006</v>
       </c>
-      <c r="J82" s="4">
+      <c r="J82" s="3">
         <v>3190170.44</v>
       </c>
       <c r="K82">
         <f t="shared" si="1"/>
         <v>50115.586578286311</v>
       </c>
-      <c r="O82" s="9"/>
-      <c r="Q82" s="9"/>
+      <c r="O82" s="7"/>
+      <c r="Q82" s="7"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
@@ -4916,59 +5914,59 @@
         <f t="shared" si="0"/>
         <v>3466502,5508320,6374910,3906161</v>
       </c>
-      <c r="I83" s="4">
+      <c r="I83" s="3">
         <v>12012</v>
       </c>
-      <c r="J83" s="4">
+      <c r="J83" s="3">
         <v>5832190.2199999997</v>
       </c>
       <c r="K83">
         <f t="shared" si="1"/>
         <v>100231.17315657262</v>
       </c>
-      <c r="O83" s="9"/>
-      <c r="Q83" s="9"/>
+      <c r="O83" s="7"/>
+      <c r="Q83" s="7"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="O84" s="9"/>
-      <c r="Q84" s="9"/>
+      <c r="O84" s="7"/>
+      <c r="Q84" s="7"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="I86" s="5"/>
+      <c r="I86" s="4"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C90" s="10"/>
-      <c r="D90" s="10"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="12"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B91">
         <v>1.0756600000000001</v>
       </c>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C93" t="s">
@@ -4979,7 +5977,7 @@
       <c r="C94">
         <v>7.7573336458901325</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4988,7 +5986,7 @@
         <f>C94*B91</f>
         <v>8.3442535095381807</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>86</v>
       </c>
     </row>
@@ -5025,28 +6023,28 @@
       <c r="B103" t="s">
         <v>1</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="3">
         <v>20047.09</v>
       </c>
-      <c r="D103" s="4">
+      <c r="D103" s="3">
         <v>32570.23</v>
       </c>
-      <c r="E103" s="4">
+      <c r="E103" s="3">
         <v>59337.98</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="3">
         <v>88896.68</v>
       </c>
-      <c r="G103" s="4">
+      <c r="G103" s="3">
         <v>631742.35</v>
       </c>
-      <c r="H103" s="4">
+      <c r="H103" s="3">
         <v>945275.96</v>
       </c>
-      <c r="I103" s="4">
+      <c r="I103" s="3">
         <v>3190170.44</v>
       </c>
-      <c r="J103" s="4">
+      <c r="J103" s="3">
         <v>5832190.2199999997</v>
       </c>
     </row>
@@ -5113,28 +6111,28 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
+        <v>90</v>
+      </c>
+      <c r="D106" t="s">
+        <v>91</v>
+      </c>
+      <c r="E106" t="s">
+        <v>92</v>
+      </c>
+      <c r="F106" t="s">
+        <v>93</v>
+      </c>
+      <c r="G106" t="s">
+        <v>94</v>
+      </c>
+      <c r="H106" t="s">
+        <v>95</v>
+      </c>
+      <c r="I106" t="s">
+        <v>96</v>
+      </c>
+      <c r="J106" t="s">
         <v>97</v>
-      </c>
-      <c r="D106" t="s">
-        <v>98</v>
-      </c>
-      <c r="E106" t="s">
-        <v>99</v>
-      </c>
-      <c r="F106" t="s">
-        <v>100</v>
-      </c>
-      <c r="G106" t="s">
-        <v>101</v>
-      </c>
-      <c r="H106" t="s">
-        <v>102</v>
-      </c>
-      <c r="I106" t="s">
-        <v>103</v>
-      </c>
-      <c r="J106" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.2">
@@ -5266,19 +6264,19 @@
       <c r="E111">
         <v>780.18770314181984</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="3">
         <v>1404.3378656552759</v>
       </c>
-      <c r="G111" s="4">
+      <c r="G111" s="3">
         <v>5011.5586578286311</v>
       </c>
-      <c r="H111" s="4">
+      <c r="H111" s="3">
         <v>10023.117315657262</v>
       </c>
-      <c r="I111" s="4">
+      <c r="I111" s="3">
         <v>50115.586578286311</v>
       </c>
-      <c r="J111" s="4">
+      <c r="J111" s="3">
         <v>100231.17315657262</v>
       </c>
     </row>
@@ -5344,35 +6342,35 @@
       <c r="B114" t="s">
         <v>23</v>
       </c>
-      <c r="C114" s="7">
+      <c r="C114" s="6">
         <f>C103</f>
         <v>20047.09</v>
       </c>
-      <c r="D114" s="7">
+      <c r="D114" s="6">
         <f>D103</f>
         <v>32570.23</v>
       </c>
-      <c r="E114" s="7">
+      <c r="E114" s="6">
         <f t="shared" ref="E114:J114" si="2">E103</f>
         <v>59337.98</v>
       </c>
-      <c r="F114" s="7">
+      <c r="F114" s="6">
         <f t="shared" si="2"/>
         <v>88896.68</v>
       </c>
-      <c r="G114" s="7">
+      <c r="G114" s="6">
         <f t="shared" si="2"/>
         <v>631742.35</v>
       </c>
-      <c r="H114" s="7">
+      <c r="H114" s="6">
         <f t="shared" si="2"/>
         <v>945275.96</v>
       </c>
-      <c r="I114" s="7">
+      <c r="I114" s="6">
         <f t="shared" si="2"/>
         <v>3190170.44</v>
       </c>
-      <c r="J114" s="7">
+      <c r="J114" s="6">
         <f t="shared" si="2"/>
         <v>5832190.2199999997</v>
       </c>
@@ -5408,22 +6406,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="F19:G19"/>
@@ -5433,6 +6415,22 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="H10:I10"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F64:G64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5441,605 +6439,1174 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66DAB95-499B-884C-8EAD-AAE9CFA64804}">
-  <dimension ref="A3:L73"/>
+  <dimension ref="A1:X82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B3" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B9" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B10" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B11" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B12" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="D14" s="1"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" t="s">
+        <v>115</v>
+      </c>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11">
+        <v>2002</v>
+      </c>
+      <c r="C3" s="10">
+        <v>0.1269230842590332</v>
+      </c>
+      <c r="D3" s="10">
+        <v>11.172725677490234</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="9"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11">
+        <v>2003</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0.12987013161182404</v>
+      </c>
+      <c r="D4" s="10">
+        <v>10.837315559387207</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="9"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11">
+        <v>2004</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0.13451708853244781</v>
+      </c>
+      <c r="D5" s="10">
+        <v>9.9093914031982422</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="9"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11">
+        <v>2005</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.13451708853244781</v>
+      </c>
+      <c r="D6" s="10">
+        <v>9.6791591644287109</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="9"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11">
+        <v>2006</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0.1349206417798996</v>
+      </c>
+      <c r="D7" s="10">
+        <v>9.8771286010742188</v>
+      </c>
+      <c r="E7" s="10">
+        <v>6.1105499694598379E-2</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0.12325375889624726</v>
+      </c>
+      <c r="W7" s="8"/>
+      <c r="X7" s="9"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11">
+        <v>2007</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.1349206417798996</v>
+      </c>
+      <c r="D8" s="10">
+        <v>9.7870693206787109</v>
+      </c>
+      <c r="E8" s="10">
+        <v>3.8151803392585892E-2</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0.10193326586720314</v>
+      </c>
+      <c r="W8" s="8"/>
+      <c r="X8" s="9"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11">
+        <v>2008</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.1411290317773819</v>
+      </c>
+      <c r="D9" s="10">
+        <v>9.3812465667724609</v>
+      </c>
+      <c r="E9" s="10">
+        <v>4.7983347643295732E-2</v>
+      </c>
+      <c r="F9" s="10">
+        <v>5.4770283631768876E-2</v>
+      </c>
+      <c r="W9" s="8"/>
+      <c r="X9" s="9"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11">
+        <v>2009</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.13804714381694794</v>
+      </c>
+      <c r="D10" s="10">
+        <v>9.0643024444580078</v>
+      </c>
+      <c r="E10" s="10">
+        <v>2.5904005422391314E-2</v>
+      </c>
+      <c r="F10" s="10">
+        <v>6.5631143509141343E-2</v>
+      </c>
+      <c r="W10" s="8"/>
+      <c r="X10" s="9"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11">
+        <v>2010</v>
+      </c>
+      <c r="C11" s="10">
+        <v>0.14093959331512451</v>
+      </c>
+      <c r="D11" s="10">
+        <v>7.4998297691345215</v>
+      </c>
+      <c r="E11" s="10">
+        <v>4.364461545080673E-2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.27534151926186201</v>
+      </c>
+      <c r="W11" s="8"/>
+      <c r="X11" s="9"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11">
+        <v>2011</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0.14417177438735962</v>
+      </c>
+      <c r="D12" s="10">
+        <v>6.436070442199707</v>
+      </c>
+      <c r="E12" s="10">
+        <v>6.6318699426575603E-2</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0.41914388325480922</v>
+      </c>
+      <c r="W12" s="8"/>
+      <c r="X12" s="9"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11">
+        <v>2012</v>
+      </c>
+      <c r="C13" s="10">
+        <v>0.1484375</v>
+      </c>
+      <c r="D13" s="10">
+        <v>5.5148839950561523</v>
+      </c>
+      <c r="E13" s="10">
+        <v>5.0489403328371575E-2</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0.53126203238968384</v>
+      </c>
+      <c r="W13" s="8"/>
+      <c r="X13" s="9"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11">
+        <v>2013</v>
+      </c>
+      <c r="C14" s="10">
+        <v>0.15408805012702942</v>
+      </c>
+      <c r="D14" s="10">
+        <v>4.514430046081543</v>
+      </c>
+      <c r="E14" s="10">
+        <v>0.10992894441648131</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0.69706494756796233</v>
+      </c>
+      <c r="W14" s="8"/>
+      <c r="X14" s="9"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11">
+        <v>2014</v>
+      </c>
+      <c r="C15" s="10">
+        <v>0.15740740299224854</v>
+      </c>
+      <c r="D15" s="10">
+        <v>4.0100564956665039</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0.11050598548795203</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.62607499292182145</v>
+      </c>
+      <c r="W15" s="8"/>
+      <c r="X15" s="9"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11">
+        <v>2015</v>
+      </c>
+      <c r="C16" s="10">
+        <v>0.16352201998233795</v>
+      </c>
+      <c r="D16" s="10">
+        <v>3.8071515560150146</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0.12594219370728657</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.5250368876622401</v>
+      </c>
+      <c r="W16" s="8"/>
+      <c r="X16" s="9"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11">
+        <v>2016</v>
+      </c>
+      <c r="C17" s="10">
+        <v>0.16459627449512482</v>
+      </c>
+      <c r="D17" s="10">
+        <v>3.553325891494751</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0.10333166007089375</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0.43956658230158402</v>
+      </c>
+      <c r="W17" s="8"/>
+      <c r="X17" s="9"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11">
+        <v>2017</v>
+      </c>
+      <c r="C18" s="10">
+        <v>0.17378048598766327</v>
+      </c>
+      <c r="D18" s="10">
+        <v>3.2257852554321289</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0.12026873487942276</v>
+      </c>
+      <c r="F18" s="10">
+        <v>0.3361025325943881</v>
+      </c>
+      <c r="W18" s="8"/>
+      <c r="X18" s="9"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11">
+        <v>2018</v>
+      </c>
+      <c r="C19" s="10">
+        <v>0.1840490847826004</v>
+      </c>
+      <c r="D19" s="10">
+        <v>2.9942643642425537</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0.15636511929143679</v>
+      </c>
+      <c r="F19" s="10">
+        <v>0.29210674980452012</v>
+      </c>
+      <c r="W19" s="8"/>
+      <c r="X19" s="9"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2" t="s">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
+      <c r="F32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B33" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B34" s="2">
+      <c r="F33">
+        <v>1.0756600000000001</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B34" s="1">
         <v>2010</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="1">
         <v>27.1</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="1">
         <v>25.6</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B35" s="2">
+      <c r="H34" s="1">
+        <v>2010</v>
+      </c>
+      <c r="I34" s="1">
+        <f>D34*$F$33</f>
+        <v>27.536896000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B35" s="1">
         <v>2011</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="1">
         <v>24</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>23.5</v>
       </c>
       <c r="E35">
         <f>-LN(D35/D34)</f>
         <v>8.5591930335403507E-2</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B36" s="2">
+      <c r="H35" s="1">
+        <v>2011</v>
+      </c>
+      <c r="I35" s="1">
+        <f t="shared" ref="I35:I46" si="0">D35*$F$33</f>
+        <v>25.278010000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B36" s="1">
         <v>2012</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="1">
         <v>23.4</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="1">
         <v>18.2</v>
       </c>
       <c r="E36">
-        <f t="shared" ref="E36:E46" si="0">-LN(D36/D35)</f>
+        <f t="shared" ref="E36:E46" si="1">-LN(D36/D35)</f>
         <v>0.25557882706736362</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B37" s="2">
+      <c r="H36" s="1">
+        <v>2012</v>
+      </c>
+      <c r="I36" s="1">
+        <f t="shared" si="0"/>
+        <v>19.577012</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B37" s="1">
         <v>2013</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="1">
         <v>22.9</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>15.4</v>
       </c>
       <c r="E37">
+        <f t="shared" si="1"/>
+        <v>0.16705408466316607</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2013</v>
+      </c>
+      <c r="I37" s="1">
         <f t="shared" si="0"/>
-        <v>0.16705408466316607</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B38" s="2">
+        <v>16.565164000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B38" s="1">
         <v>2014</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="1">
         <v>22.4</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="1">
         <v>13.7</v>
       </c>
       <c r="E38">
+        <f t="shared" si="1"/>
+        <v>0.11697167658550435</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2014</v>
+      </c>
+      <c r="I38" s="1">
         <f t="shared" si="0"/>
-        <v>0.11697167658550435</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B39" s="2">
+        <v>14.736542</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B39" s="1">
         <v>2015</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="1">
         <v>21.7</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="1">
         <v>12.4</v>
       </c>
       <c r="E39">
+        <f t="shared" si="1"/>
+        <v>9.9699360223087924E-2</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2015</v>
+      </c>
+      <c r="I39" s="1">
         <f t="shared" si="0"/>
-        <v>9.9699360223087924E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B40" s="2">
+        <v>13.338184000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B40" s="1">
         <v>2016</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="1">
         <v>21.1</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="1">
         <v>11.3</v>
       </c>
       <c r="E40">
+        <f t="shared" si="1"/>
+        <v>9.2893746892696208E-2</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2016</v>
+      </c>
+      <c r="I40" s="1">
         <f t="shared" si="0"/>
-        <v>9.2893746892696208E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B41" s="2">
+        <v>12.154958000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B41" s="1">
         <v>2017</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="1">
         <v>21.5</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="1">
         <v>10.9</v>
       </c>
       <c r="E41">
+        <f t="shared" si="1"/>
+        <v>3.6039936483196928E-2</v>
+      </c>
+      <c r="H41" s="1">
+        <v>2017</v>
+      </c>
+      <c r="I41" s="1">
         <f t="shared" si="0"/>
-        <v>3.6039936483196928E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B42" s="2">
+        <v>11.724694000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B42" s="1">
         <v>2018</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="1">
         <v>20.100000000000001</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="1">
         <v>10.4</v>
       </c>
       <c r="E42">
+        <f t="shared" si="1"/>
+        <v>4.6956983087770979E-2</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2018</v>
+      </c>
+      <c r="I42" s="1">
         <f t="shared" si="0"/>
-        <v>4.6956983087770979E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B43" s="2">
+        <v>11.186864000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B43" s="1">
         <v>2019</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="1">
         <v>19.2</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>9.9</v>
       </c>
       <c r="E43">
+        <f t="shared" si="1"/>
+        <v>4.9271049006782794E-2</v>
+      </c>
+      <c r="H43" s="1">
+        <v>2019</v>
+      </c>
+      <c r="I43" s="1">
         <f t="shared" si="0"/>
-        <v>4.9271049006782794E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B44" s="2">
+        <v>10.649034</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B44" s="1">
         <v>2020</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="1">
         <v>18.2</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="1">
         <v>9.6</v>
       </c>
       <c r="E44">
+        <f t="shared" si="1"/>
+        <v>3.0771658666753774E-2</v>
+      </c>
+      <c r="H44" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I44" s="1">
         <f t="shared" si="0"/>
-        <v>3.0771658666753774E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B45" s="2">
+        <v>10.326336</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B45" s="1">
         <v>2021</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="1">
         <v>18.2</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>9.6</v>
       </c>
       <c r="E45">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I45" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B46" s="2">
+        <v>10.326336</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B46" s="1">
         <v>2022</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="1">
         <v>17.8</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="1">
         <v>9.1999999999999993</v>
       </c>
       <c r="E46">
+        <f t="shared" si="1"/>
+        <v>4.2559614418796007E-2</v>
+      </c>
+      <c r="H46" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I46" s="1">
         <f t="shared" si="0"/>
-        <v>4.2559614418796007E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
+        <v>9.8960720000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D47">
         <f>D46*$F$50</f>
-        <v>8.4479269375503723</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
+        <v>8.7532883435133044</v>
+      </c>
+      <c r="H47" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I47" s="1">
+        <f>I46*$F$50</f>
+        <v>9.4155621395835229</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D48">
-        <f t="shared" ref="D48:D52" si="1">D47*$F$50</f>
-        <v>7.7573336458901325</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+        <f t="shared" ref="D48:D52" si="2">D47*$F$50</f>
+        <v>8.3282670461615105</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I48" s="1">
+        <f t="shared" ref="I48:I64" si="3">I47*$F$50</f>
+        <v>8.9583837308740915</v>
+      </c>
+    </row>
+    <row r="49" spans="4:9" x14ac:dyDescent="0.2">
       <c r="D49">
-        <f t="shared" si="1"/>
-        <v>7.1231943337696846</v>
+        <f t="shared" si="2"/>
+        <v>7.9238829192208193</v>
       </c>
       <c r="F49">
-        <f>AVERAGE(E35:E46)</f>
-        <v>8.5282405619210189E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+        <f>AVERAGE(E39:E46)</f>
+        <v>4.9774043597385582E-2</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I49" s="1">
+        <f t="shared" si="3"/>
+        <v>8.5234039008890665</v>
+      </c>
+    </row>
+    <row r="50" spans="4:9" x14ac:dyDescent="0.2">
       <c r="D50">
-        <f t="shared" si="1"/>
-        <v>6.5408940536585982</v>
+        <f t="shared" si="2"/>
+        <v>7.5391339121934546</v>
       </c>
       <c r="F50">
         <f>EXP(-F49)</f>
-        <v>0.91825292799460578</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.9514443851644897</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2026</v>
+      </c>
+      <c r="I50" s="1">
+        <f t="shared" si="3"/>
+        <v>8.1095447839900103</v>
+      </c>
+    </row>
+    <row r="51" spans="4:9" x14ac:dyDescent="0.2">
       <c r="D51">
-        <f t="shared" si="1"/>
-        <v>6.0061951164745135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>7.1730666297596555</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2027</v>
+      </c>
+      <c r="I51" s="1">
+        <f t="shared" si="3"/>
+        <v>7.7157808509672696</v>
+      </c>
+    </row>
+    <row r="52" spans="4:9" x14ac:dyDescent="0.2">
       <c r="D52">
-        <f t="shared" si="1"/>
-        <v>5.5152062518096248</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C57" t="s">
+        <f t="shared" si="2"/>
+        <v>6.8247739692955935</v>
+      </c>
+      <c r="H52" s="1">
+        <v>2028</v>
+      </c>
+      <c r="I52" s="1">
+        <f t="shared" si="3"/>
+        <v>7.3411363678124966</v>
+      </c>
+    </row>
+    <row r="53" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H53" s="1">
+        <v>2029</v>
+      </c>
+      <c r="I53" s="1">
+        <f t="shared" si="3"/>
+        <v>6.9846829778820361</v>
+      </c>
+    </row>
+    <row r="54" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H54" s="1">
+        <v>2030</v>
+      </c>
+      <c r="I54" s="1">
+        <f t="shared" si="3"/>
+        <v>6.6455374014598512</v>
+      </c>
+    </row>
+    <row r="55" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H55" s="1">
+        <v>2031</v>
+      </c>
+      <c r="I55" s="1">
+        <f t="shared" si="3"/>
+        <v>6.322859247019589</v>
+      </c>
+    </row>
+    <row r="56" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H56" s="1">
+        <v>2032</v>
+      </c>
+      <c r="I56" s="1">
+        <f t="shared" si="3"/>
+        <v>6.0158489287621615</v>
+      </c>
+    </row>
+    <row r="57" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H57" s="1">
+        <v>2033</v>
+      </c>
+      <c r="I57" s="1">
+        <f t="shared" si="3"/>
+        <v>5.7237456852685691</v>
+      </c>
+    </row>
+    <row r="58" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H58" s="1">
+        <v>2034</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="3"/>
+        <v>5.4458256943582546</v>
+      </c>
+    </row>
+    <row r="59" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H59" s="1">
+        <v>2035</v>
+      </c>
+      <c r="I59" s="1">
+        <f t="shared" si="3"/>
+        <v>5.1814002794816698</v>
+      </c>
+    </row>
+    <row r="60" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H60" s="1">
+        <v>2036</v>
+      </c>
+      <c r="I60" s="1">
+        <f t="shared" si="3"/>
+        <v>4.929814203202552</v>
+      </c>
+    </row>
+    <row r="61" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H61" s="1">
+        <v>2037</v>
+      </c>
+      <c r="I61" s="1">
+        <f t="shared" si="3"/>
+        <v>4.6904440435412207</v>
+      </c>
+    </row>
+    <row r="62" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H62" s="1">
+        <v>2038</v>
+      </c>
+      <c r="I62" s="1">
+        <f t="shared" si="3"/>
+        <v>4.4626966491555198</v>
+      </c>
+    </row>
+    <row r="63" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H63" s="1">
+        <v>2039</v>
+      </c>
+      <c r="I63" s="1">
+        <f t="shared" si="3"/>
+        <v>4.2460076695314015</v>
+      </c>
+    </row>
+    <row r="64" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="H64" s="1">
+        <v>2040</v>
+      </c>
+      <c r="I64" s="1">
+        <f t="shared" si="3"/>
+        <v>4.039840156541012</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C66" t="s">
+        <v>99</v>
+      </c>
+      <c r="D66" t="s">
+        <v>104</v>
+      </c>
+      <c r="E66" t="s">
+        <v>105</v>
+      </c>
+      <c r="F66" t="s">
         <v>106</v>
       </c>
-      <c r="D57" t="s">
-        <v>111</v>
-      </c>
-      <c r="E57" t="s">
-        <v>112</v>
-      </c>
-      <c r="F57" t="s">
-        <v>113</v>
-      </c>
-      <c r="G57" t="s">
-        <v>114</v>
-      </c>
-      <c r="H57" t="s">
-        <v>115</v>
-      </c>
-      <c r="I57" t="s">
-        <v>116</v>
-      </c>
-      <c r="J57" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+      <c r="G66" t="s">
         <v>107</v>
       </c>
-      <c r="C58">
+      <c r="H66" t="s">
+        <v>108</v>
+      </c>
+      <c r="I66" t="s">
+        <v>109</v>
+      </c>
+      <c r="J66" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>100</v>
+      </c>
+      <c r="C67">
         <f>3179+1951</f>
         <v>5130</v>
       </c>
-      <c r="D58">
+      <c r="D67">
         <f>6358+1952</f>
         <v>8310</v>
       </c>
-      <c r="E58">
+      <c r="E67">
         <f>15895+3904</f>
         <v>19799</v>
       </c>
-      <c r="F58">
+      <c r="F67">
         <f>28611+5856</f>
         <v>34467</v>
       </c>
-      <c r="G58">
+      <c r="G67">
         <f>102102+11536</f>
         <v>113638</v>
       </c>
-      <c r="H58">
+      <c r="H67">
         <f>204204+23072</f>
         <v>227276</v>
       </c>
-      <c r="I58">
+      <c r="I67">
         <f>1021020+115360</f>
         <v>1136380</v>
       </c>
-      <c r="J58">
+      <c r="J67">
         <f>2042040+230720</f>
         <v>2272760</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>108</v>
-      </c>
-      <c r="C59">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68">
         <v>10941</v>
       </c>
-      <c r="D59">
+      <c r="D68">
         <v>19651</v>
       </c>
-      <c r="E59">
+      <c r="E68">
         <v>35396</v>
       </c>
-      <c r="F59">
+      <c r="F68">
         <v>53924</v>
       </c>
-      <c r="G59">
+      <c r="G68">
         <v>323503</v>
       </c>
-      <c r="H59">
+      <c r="H68">
         <v>505567</v>
       </c>
-      <c r="I59">
+      <c r="I68">
         <v>1966399</v>
       </c>
-      <c r="J59">
+      <c r="J68">
         <v>3681480</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>109</v>
-      </c>
-      <c r="C60">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>102</v>
+      </c>
+      <c r="C69">
         <v>16989</v>
       </c>
-      <c r="D60">
+      <c r="D69">
         <v>27601</v>
       </c>
-      <c r="E60">
+      <c r="E69">
         <v>50286</v>
       </c>
-      <c r="F60">
+      <c r="F69">
         <v>75336</v>
       </c>
-      <c r="G60">
+      <c r="G69">
         <v>535374</v>
       </c>
-      <c r="H60">
+      <c r="H69">
         <v>801081</v>
       </c>
-      <c r="I60">
+      <c r="I69">
         <v>2703534</v>
       </c>
-      <c r="J60">
+      <c r="J69">
         <v>4942534</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>110</v>
-      </c>
-      <c r="C61">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>103</v>
+      </c>
+      <c r="C70">
         <v>20047</v>
       </c>
-      <c r="D61">
+      <c r="D70">
         <v>32570</v>
       </c>
-      <c r="E61">
+      <c r="E70">
         <v>59338</v>
       </c>
-      <c r="F61">
+      <c r="F70">
         <v>88897</v>
       </c>
-      <c r="G61">
+      <c r="G70">
         <v>631742</v>
       </c>
-      <c r="H61">
+      <c r="H70">
         <v>945276</v>
       </c>
-      <c r="I61">
+      <c r="I70">
         <v>3190170</v>
       </c>
-      <c r="J61">
+      <c r="J70">
         <v>5832190</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>107</v>
-      </c>
-      <c r="C65">
-        <f>C58/C$61</f>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>100</v>
+      </c>
+      <c r="C74">
+        <f>C67/C$70</f>
         <v>0.25589863820022946</v>
       </c>
-      <c r="D65">
-        <f t="shared" ref="D65:J65" si="2">D58/D$61</f>
+      <c r="D74">
+        <f t="shared" ref="D74:J74" si="4">D67/D$70</f>
         <v>0.25514276941971137</v>
       </c>
-      <c r="E65">
-        <f t="shared" si="2"/>
+      <c r="E74">
+        <f t="shared" si="4"/>
         <v>0.33366476793960026</v>
       </c>
-      <c r="F65">
-        <f t="shared" si="2"/>
+      <c r="F74">
+        <f t="shared" si="4"/>
         <v>0.38771837069867376</v>
       </c>
-      <c r="G65">
-        <f t="shared" si="2"/>
+      <c r="G74">
+        <f t="shared" si="4"/>
         <v>0.17988039421156105</v>
       </c>
-      <c r="H65">
-        <f t="shared" si="2"/>
+      <c r="H74">
+        <f t="shared" si="4"/>
         <v>0.24043348186138228</v>
       </c>
-      <c r="I65">
-        <f t="shared" si="2"/>
+      <c r="I74">
+        <f t="shared" si="4"/>
         <v>0.3562129917841369</v>
       </c>
-      <c r="J65">
-        <f t="shared" si="2"/>
+      <c r="J74">
+        <f t="shared" si="4"/>
         <v>0.38969237970642245</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>108</v>
-      </c>
-      <c r="C66">
-        <f t="shared" ref="C66:J67" si="3">C59/C$61</f>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>101</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:J76" si="5">C68/C$70</f>
         <v>0.54576744650072329</v>
       </c>
-      <c r="D66">
-        <f t="shared" si="3"/>
+      <c r="D75">
+        <f t="shared" si="5"/>
         <v>0.60334663801043908</v>
       </c>
-      <c r="E66">
-        <f t="shared" si="3"/>
+      <c r="E75">
+        <f t="shared" si="5"/>
         <v>0.59651488085206783</v>
       </c>
-      <c r="F66">
-        <f t="shared" si="3"/>
+      <c r="F75">
+        <f t="shared" si="5"/>
         <v>0.60658964869455667</v>
       </c>
-      <c r="G66">
-        <f t="shared" si="3"/>
+      <c r="G75">
+        <f t="shared" si="5"/>
         <v>0.51208088111919103</v>
       </c>
-      <c r="H66">
-        <f t="shared" si="3"/>
+      <c r="H75">
+        <f t="shared" si="5"/>
         <v>0.53483532851780857</v>
       </c>
-      <c r="I66">
-        <f t="shared" si="3"/>
+      <c r="I75">
+        <f t="shared" si="5"/>
         <v>0.61639317026992291</v>
       </c>
-      <c r="J66">
-        <f t="shared" si="3"/>
+      <c r="J75">
+        <f t="shared" si="5"/>
         <v>0.63123457912036474</v>
       </c>
-      <c r="K66">
-        <f>AVERAGE(C66:J66)</f>
+      <c r="K75">
+        <f>AVERAGE(C75:J75)</f>
         <v>0.58084532163563429</v>
       </c>
-      <c r="L66">
+      <c r="L75">
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>109</v>
-      </c>
-      <c r="C67">
-        <f t="shared" si="3"/>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>102</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="5"/>
         <v>0.84745847258941487</v>
       </c>
-      <c r="D67">
-        <f t="shared" si="3"/>
+      <c r="D76">
+        <f t="shared" si="5"/>
         <v>0.84743629106539764</v>
       </c>
-      <c r="E67">
-        <f t="shared" si="3"/>
+      <c r="E76">
+        <f t="shared" si="5"/>
         <v>0.84745020054602449</v>
       </c>
-      <c r="F67">
-        <f t="shared" si="3"/>
+      <c r="F76">
+        <f t="shared" si="5"/>
         <v>0.84745266994386759</v>
       </c>
-      <c r="G67">
-        <f t="shared" si="3"/>
+      <c r="G76">
+        <f t="shared" si="5"/>
         <v>0.8474567149247636</v>
       </c>
-      <c r="H67">
-        <f t="shared" si="3"/>
+      <c r="H76">
+        <f t="shared" si="5"/>
         <v>0.84745725058078281</v>
       </c>
-      <c r="I67">
-        <f t="shared" si="3"/>
+      <c r="I76">
+        <f t="shared" si="5"/>
         <v>0.84745765899622905</v>
       </c>
-      <c r="J67">
-        <f t="shared" si="3"/>
+      <c r="J76">
+        <f t="shared" si="5"/>
         <v>0.84745764455547568</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="K72">
-        <f>1-K66</f>
+    <row r="81" spans="11:12" x14ac:dyDescent="0.2">
+      <c r="K81">
+        <f>1-K75</f>
         <v>0.41915467836436571</v>
       </c>
-      <c r="L72">
-        <f>1-L66</f>
+      <c r="L81">
+        <f>1-L75</f>
         <v>0.42000000000000004</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="K73">
-        <f>K72/25</f>
+    <row r="82" spans="11:12" x14ac:dyDescent="0.2">
+      <c r="K82">
+        <f>K81/25</f>
         <v>1.6766187134574628E-2</v>
       </c>
-      <c r="L73">
-        <f>L72/25</f>
+      <c r="L82">
+        <f>L81/25</f>
         <v>1.6800000000000002E-2</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="W1:X1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
